--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 4.567,90</t>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R$ 4.558,43</t>
   </si>
   <si>
     <t>51.2</t>
@@ -947,7 +947,7 @@
     <t>32.6</t>
   </si>
   <si>
-    <t>4.99</t>
+    <t>5.00</t>
   </si>
   <si>
     <t>18.6</t>
@@ -959,7 +959,7 @@
     <t>6.0</t>
   </si>
   <si>
-    <t>43.1%</t>
+    <t>43.2%</t>
   </si>
   <si>
     <t>20.1%</t>
@@ -30839,7 +30839,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -30869,14 +30869,26 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
+      <c r="M199" s="5">
+        <v>2873.54</v>
+      </c>
+      <c r="N199" s="6">
+        <v>34</v>
+      </c>
       <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
+      <c r="P199" s="7">
+        <v>5.4600999999999997</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>17.853124999999999</v>
+      </c>
+      <c r="R199" s="8">
+        <v>4.8770812499999998</v>
+      </c>
       <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
+      <c r="T199" s="9">
+        <v>0.25</v>
+      </c>
       <c r="U199" s="9"/>
       <c r="V199" s="9"/>
       <c r="W199" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -935,16 +935,16 @@
     <t>214</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 4.558,43</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 4.561,45</t>
   </si>
   <si>
     <t>51.2</t>
   </si>
   <si>
-    <t>32.6</t>
+    <t>32.5</t>
   </si>
   <si>
     <t>5.00</t>
@@ -953,16 +953,16 @@
     <t>18.6</t>
   </si>
   <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>43.2%</t>
-  </si>
-  <si>
-    <t>20.1%</t>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>42.7%</t>
+  </si>
+  <si>
+    <t>20.0%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -971,13 +971,13 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.5%</t>
+    <t>5.4%</t>
   </si>
   <si>
     <t>1.2%</t>
   </si>
   <si>
-    <t>7.8%</t>
+    <t>7.7%</t>
   </si>
   <si>
     <t>2.6%</t>
@@ -986,10 +986,10 @@
     <t>5.6%</t>
   </si>
   <si>
-    <t>1448.0</t>
-  </si>
-  <si>
-    <t>1163.0</t>
+    <t>1454.0</t>
+  </si>
+  <si>
+    <t>1169.0</t>
   </si>
   <si>
     <t>93.0</t>
@@ -1010,16 +1010,16 @@
     <t>448.0</t>
   </si>
   <si>
-    <t>149.0</t>
-  </si>
-  <si>
-    <t>322.0</t>
+    <t>150.0</t>
+  </si>
+  <si>
+    <t>326.0</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>38.0</t>
+    <t>39.0</t>
   </si>
   <si>
     <t>1</t>
@@ -7664,7 +7664,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7694,35 +7694,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>5102.0299999999997</v>
+      </c>
+      <c r="N42" s="6">
+        <v>56</v>
+      </c>
+      <c r="O42" s="6">
+        <v>40</v>
+      </c>
+      <c r="P42" s="7">
+        <v>5.3173076923076925</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>18.749582499999999</v>
+      </c>
+      <c r="R42" s="8">
+        <v>6.0870825000000002</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -20010,7 +20068,9 @@
       <c r="N126" s="6">
         <v>33</v>
       </c>
-      <c r="O126" s="6"/>
+      <c r="O126" s="6">
+        <v>25</v>
+      </c>
       <c r="P126" s="7">
         <v>5.841176470588235</v>
       </c>
@@ -20020,31 +20080,75 @@
       <c r="R126" s="8">
         <v>14.118668</v>
       </c>
-      <c r="S126" s="8"/>
+      <c r="S126" s="8">
+        <v>7</v>
+      </c>
       <c r="T126" s="9">
         <v>0.040000000000000001</v>
       </c>
-      <c r="U126" s="9"/>
-      <c r="V126" s="9"/>
-      <c r="W126" s="9"/>
-      <c r="X126" s="9"/>
-      <c r="Y126" s="9"/>
-      <c r="Z126" s="9"/>
-      <c r="AA126" s="9"/>
-      <c r="AB126" s="9"/>
-      <c r="AC126" s="9"/>
-      <c r="AD126" s="6"/>
-      <c r="AE126" s="6"/>
-      <c r="AF126" s="6"/>
-      <c r="AG126" s="6"/>
-      <c r="AH126" s="6"/>
-      <c r="AI126" s="6"/>
-      <c r="AJ126" s="6"/>
-      <c r="AK126" s="6"/>
-      <c r="AL126" s="6"/>
-      <c r="AM126" s="6"/>
-      <c r="AN126" s="9"/>
-      <c r="AO126" s="6"/>
+      <c r="U126" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V126" s="9">
+        <v>0</v>
+      </c>
+      <c r="W126" s="9">
+        <v>0</v>
+      </c>
+      <c r="X126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y126" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB126" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AC126" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AD126" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM126" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN126" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO126" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
       </c>
@@ -30875,7 +30979,9 @@
       <c r="N199" s="6">
         <v>34</v>
       </c>
-      <c r="O199" s="6"/>
+      <c r="O199" s="6">
+        <v>16</v>
+      </c>
       <c r="P199" s="7">
         <v>5.4600999999999997</v>
       </c>
@@ -30885,31 +30991,75 @@
       <c r="R199" s="8">
         <v>4.8770812499999998</v>
       </c>
-      <c r="S199" s="8"/>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
       <c r="T199" s="9">
         <v>0.25</v>
       </c>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="U199" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 4.561,45</t>
-  </si>
-  <si>
-    <t>51.2</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 4.558,27</t>
+  </si>
+  <si>
+    <t>51.1</t>
   </si>
   <si>
     <t>32.5</t>
   </si>
   <si>
-    <t>5.00</t>
+    <t>5.01</t>
   </si>
   <si>
     <t>18.6</t>
   </si>
   <si>
-    <t>7.0</t>
+    <t>7.1</t>
   </si>
   <si>
     <t>6.1</t>
   </si>
   <si>
-    <t>42.7%</t>
+    <t>42.6%</t>
   </si>
   <si>
     <t>20.0%</t>
@@ -980,40 +980,40 @@
     <t>7.7%</t>
   </si>
   <si>
-    <t>2.6%</t>
+    <t>2.5%</t>
   </si>
   <si>
     <t>5.6%</t>
   </si>
   <si>
-    <t>1454.0</t>
-  </si>
-  <si>
-    <t>1169.0</t>
+    <t>1471.0</t>
+  </si>
+  <si>
+    <t>1179.0</t>
   </si>
   <si>
     <t>93.0</t>
   </si>
   <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>316.0</t>
-  </si>
-  <si>
-    <t>68.0</t>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>318.0</t>
+  </si>
+  <si>
+    <t>72.0</t>
   </si>
   <si>
     <t>14.0</t>
   </si>
   <si>
-    <t>448.0</t>
+    <t>455.0</t>
   </si>
   <si>
     <t>150.0</t>
   </si>
   <si>
-    <t>326.0</t>
+    <t>330.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -16570,7 +16570,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16600,35 +16600,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>3985</v>
+      </c>
+      <c r="N102" s="6">
+        <v>35</v>
+      </c>
+      <c r="O102" s="6">
+        <v>28</v>
+      </c>
+      <c r="P102" s="7">
+        <v>7.3761270270270272</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>24.269046428571432</v>
+      </c>
+      <c r="R102" s="8">
+        <v>13.843940909090911</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.21428571428571427</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.035714285714000003</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -932,19 +932,22 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 4.558,27</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>32.5</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.579,48</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>32.7</t>
   </si>
   <si>
     <t>5.01</t>
@@ -956,16 +959,16 @@
     <t>7.1</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>20.0%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>19.8%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -974,7 +977,7 @@
     <t>5.4%</t>
   </si>
   <si>
-    <t>1.2%</t>
+    <t>1.3%</t>
   </si>
   <si>
     <t>7.7%</t>
@@ -983,43 +986,43 @@
     <t>2.5%</t>
   </si>
   <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>1471.0</t>
-  </si>
-  <si>
-    <t>1179.0</t>
-  </si>
-  <si>
-    <t>93.0</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
-    <t>318.0</t>
-  </si>
-  <si>
-    <t>72.0</t>
+    <t>5.5%</t>
+  </si>
+  <si>
+    <t>1509.0</t>
+  </si>
+  <si>
+    <t>1204.0</t>
+  </si>
+  <si>
+    <t>94.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>327.0</t>
+  </si>
+  <si>
+    <t>76.0</t>
   </si>
   <si>
     <t>14.0</t>
   </si>
   <si>
-    <t>455.0</t>
-  </si>
-  <si>
-    <t>150.0</t>
-  </si>
-  <si>
-    <t>330.0</t>
+    <t>469.0</t>
+  </si>
+  <si>
+    <t>153.0</t>
+  </si>
+  <si>
+    <t>336.0</t>
   </si>
   <si>
     <t>0.7%</t>
   </si>
   <si>
-    <t>39.0</t>
+    <t>40.0</t>
   </si>
   <si>
     <t>1</t>
@@ -6468,7 +6471,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -6498,35 +6501,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>9011.8600000000006</v>
+      </c>
+      <c r="N34" s="6">
+        <v>111</v>
+      </c>
+      <c r="O34" s="6">
+        <v>69</v>
+      </c>
+      <c r="P34" s="7">
+        <v>7.5350961538461538</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>16.569323188405797</v>
+      </c>
+      <c r="R34" s="8">
+        <v>2.7719811594202897</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.014492753623188406</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -12742,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12770,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>6626.8299999999999</v>
+      </c>
+      <c r="N76" s="6">
+        <v>86</v>
+      </c>
+      <c r="O76" s="6">
+        <v>46</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.1384615384615389</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>22.07463695652174</v>
+      </c>
+      <c r="R76" s="8">
+        <v>13.313513513513515</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.41304347826086957</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.32608695652173914</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0.021739130434000001</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.13043478260869565</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.2391304347826087</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>25</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -18616,33 +18735,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>22</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -22383,7 +22548,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>51</v>
@@ -22413,35 +22578,93 @@
         <v>58</v>
       </c>
       <c r="L141" s="4"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="6"/>
-      <c r="O141" s="6"/>
-      <c r="P141" s="7"/>
-      <c r="Q141" s="8"/>
-      <c r="R141" s="8"/>
-      <c r="S141" s="8"/>
-      <c r="T141" s="9"/>
-      <c r="U141" s="9"/>
-      <c r="V141" s="9"/>
-      <c r="W141" s="9"/>
-      <c r="X141" s="9"/>
-      <c r="Y141" s="9"/>
-      <c r="Z141" s="9"/>
-      <c r="AA141" s="9"/>
-      <c r="AB141" s="9"/>
-      <c r="AC141" s="9"/>
-      <c r="AD141" s="6"/>
-      <c r="AE141" s="6"/>
-      <c r="AF141" s="6"/>
-      <c r="AG141" s="6"/>
-      <c r="AH141" s="6"/>
-      <c r="AI141" s="6"/>
-      <c r="AJ141" s="6"/>
-      <c r="AK141" s="6"/>
-      <c r="AL141" s="6"/>
-      <c r="AM141" s="6"/>
-      <c r="AN141" s="9"/>
-      <c r="AO141" s="6"/>
+      <c r="M141" s="5">
+        <v>1939.6099999999999</v>
+      </c>
+      <c r="N141" s="6">
+        <v>21</v>
+      </c>
+      <c r="O141" s="6">
+        <v>12</v>
+      </c>
+      <c r="P141" s="7">
+        <v>3.6614052631578944</v>
+      </c>
+      <c r="Q141" s="8">
+        <v>14.909725</v>
+      </c>
+      <c r="R141" s="8">
+        <v>3.4291666666666667</v>
+      </c>
+      <c r="S141" s="8">
+        <v>8</v>
+      </c>
+      <c r="T141" s="9">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="U141" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="V141" s="9">
+        <v>0</v>
+      </c>
+      <c r="W141" s="9">
+        <v>0</v>
+      </c>
+      <c r="X141" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y141" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AC141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL141" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN141" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO141" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP141" s="4">
         <v>58</v>
       </c>
@@ -33200,137 +33423,282 @@
       </c>
     </row>
     <row r="216" ht="13.5" customHeight="1">
-      <c t="s" r="A216" s="11">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>56</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>57</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>58</v>
+      </c>
+      <c r="L216" s="4"/>
+      <c r="M216" s="5"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6">
+        <v>44</v>
+      </c>
+      <c r="P216" s="7"/>
+      <c r="Q216" s="8"/>
+      <c r="R216" s="8"/>
+      <c r="S216" s="8">
+        <v>7</v>
+      </c>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9">
+        <v>0.068181818181818177</v>
+      </c>
+      <c r="V216" s="9">
+        <v>0</v>
+      </c>
+      <c r="W216" s="9">
+        <v>0</v>
+      </c>
+      <c r="X216" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y216" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Z216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA216" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AB216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC216" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD216" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE216" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK216" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL216" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM216" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN216" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO216" s="6">
+        <v>0</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>58</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>307</v>
       </c>
-      <c t="s" r="B216" s="11">
+      <c t="s" r="AS216" s="4">
+        <v>60</v>
+      </c>
+      <c t="s" r="AT216" s="4">
+        <v>61</v>
+      </c>
+      <c t="s" r="AU216" s="4">
+        <v>62</v>
+      </c>
+      <c t="s" r="AV216" s="4">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW216" s="4">
+        <v>59</v>
+      </c>
+      <c r="AX216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ216" s="10"/>
+      <c t="s" r="BA216" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="217" ht="13.5" customHeight="1">
+      <c t="s" r="A217" s="11">
         <v>308</v>
       </c>
-      <c r="C216" s="12"/>
-      <c r="D216" s="12"/>
-      <c r="E216" s="12"/>
-      <c r="F216" s="12"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="12"/>
-      <c r="I216" s="12"/>
-      <c r="J216" s="12"/>
-      <c r="K216" s="12"/>
-      <c r="L216" s="12"/>
-      <c t="s" r="M216" s="11">
+      <c t="s" r="B217" s="11">
         <v>309</v>
       </c>
-      <c t="s" r="N216" s="11">
+      <c r="C217" s="12"/>
+      <c r="D217" s="12"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
+      <c r="G217" s="12"/>
+      <c r="H217" s="12"/>
+      <c r="I217" s="12"/>
+      <c r="J217" s="12"/>
+      <c r="K217" s="12"/>
+      <c r="L217" s="12"/>
+      <c t="s" r="M217" s="11">
         <v>310</v>
       </c>
-      <c t="s" r="O216" s="11">
+      <c t="s" r="N217" s="11">
         <v>311</v>
       </c>
-      <c t="s" r="P216" s="11">
+      <c t="s" r="O217" s="11">
         <v>312</v>
       </c>
-      <c t="s" r="Q216" s="11">
+      <c t="s" r="P217" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="R216" s="11">
+      <c t="s" r="Q217" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="S216" s="11">
+      <c t="s" r="R217" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="T216" s="11">
+      <c t="s" r="S217" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="U216" s="11">
+      <c t="s" r="T217" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="V216" s="11">
+      <c t="s" r="U217" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="W216" s="11">
+      <c t="s" r="V217" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="X216" s="11">
+      <c t="s" r="W217" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="Y216" s="11">
+      <c t="s" r="X217" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="Z216" s="11">
-        <v>319</v>
-      </c>
-      <c t="s" r="AA216" s="11">
+      <c t="s" r="Y217" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AB216" s="11">
+      <c t="s" r="Z217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AA217" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AC216" s="11">
+      <c t="s" r="AB217" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AC217" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AD217" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AE217" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AF217" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AG217" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AH217" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
+      <c t="s" r="AI217" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AJ217" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AK217" s="11">
         <v>333</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AL217" s="11">
         <v>334</v>
       </c>
-      <c t="s" r="AN216" s="11">
+      <c t="s" r="AM217" s="11">
         <v>335</v>
       </c>
-      <c t="s" r="AO216" s="11">
+      <c t="s" r="AN217" s="11">
         <v>336</v>
       </c>
-      <c r="AP216" s="12"/>
-      <c t="s" r="AQ216" s="12">
-        <v>59</v>
-      </c>
-      <c r="AR216" s="12"/>
-      <c r="AS216" s="12"/>
-      <c r="AT216" s="12"/>
-      <c r="AU216" s="12"/>
-      <c t="s" r="AV216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AW216" s="12">
-        <v>59</v>
-      </c>
-      <c t="s" r="AX216" s="11">
+      <c t="s" r="AO217" s="11">
         <v>337</v>
       </c>
-      <c t="s" r="AY216" s="11">
-        <v>337</v>
-      </c>
-      <c r="AZ216" s="12"/>
-      <c r="BA216" s="12"/>
+      <c r="AP217" s="12"/>
+      <c t="s" r="AQ217" s="12">
+        <v>59</v>
+      </c>
+      <c r="AR217" s="12"/>
+      <c r="AS217" s="12"/>
+      <c r="AT217" s="12"/>
+      <c r="AU217" s="12"/>
+      <c t="s" r="AV217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AW217" s="12">
+        <v>59</v>
+      </c>
+      <c t="s" r="AX217" s="11">
+        <v>338</v>
+      </c>
+      <c t="s" r="AY217" s="11">
+        <v>338</v>
+      </c>
+      <c r="AZ217" s="12"/>
+      <c r="BA217" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BA216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:BA217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -938,13 +938,13 @@
     <t>215</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 4.579,48</t>
-  </si>
-  <si>
-    <t>51.4</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 4.582,96</t>
+  </si>
+  <si>
+    <t>51.5</t>
   </si>
   <si>
     <t>32.7</t>
@@ -962,7 +962,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>42.2%</t>
+    <t>42.4%</t>
   </si>
   <si>
     <t>19.8%</t>
@@ -25192,7 +25192,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -25222,18 +25222,30 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="5">
+        <v>5223.4399999999996</v>
+      </c>
+      <c r="N159" s="6">
+        <v>59</v>
+      </c>
       <c r="O159" s="6">
         <v>46</v>
       </c>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
+      <c r="P159" s="7">
+        <v>4.5320981481481484</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>17.075723913043479</v>
+      </c>
+      <c r="R159" s="8">
+        <v>5.4670282608695659</v>
+      </c>
       <c r="S159" s="8">
         <v>7</v>
       </c>
-      <c r="T159" s="9"/>
+      <c r="T159" s="9">
+        <v>0.32608695652173914</v>
+      </c>
       <c r="U159" s="9">
         <v>0.086956521739130432</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -938,10 +938,10 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 4.582,96</t>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 4.582,86</t>
   </si>
   <si>
     <t>51.5</t>
@@ -950,7 +950,7 @@
     <t>32.7</t>
   </si>
   <si>
-    <t>5.01</t>
+    <t>5.02</t>
   </si>
   <si>
     <t>18.6</t>
@@ -962,7 +962,7 @@
     <t>6.2</t>
   </si>
   <si>
-    <t>42.4%</t>
+    <t>42.5%</t>
   </si>
   <si>
     <t>19.8%</t>
@@ -14776,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>4564.5100000000002</v>
+      </c>
+      <c r="N89" s="6">
+        <v>47</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>7.1185613636363634</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>21.747332</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.2423624999999996</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.12</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -29098,7 +29110,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31806,7 +31818,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>
@@ -33439,7 +33451,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-08).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>28</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 4.582,86</t>
+    <t>R$ 4.537,11</t>
   </si>
   <si>
-    <t>51.5</t>
+    <t>50.9</t>
   </si>
   <si>
-    <t>32.7</t>
+    <t>32.6</t>
   </si>
   <si>
-    <t>5.02</t>
+    <t>5.04</t>
   </si>
   <si>
-    <t>18.6</t>
+    <t>18.5</t>
   </si>
   <si>
-    <t>7.1</t>
+    <t>6.9</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>42.5%</t>
+    <t>42.6%</t>
   </si>
   <si>
-    <t>19.8%</t>
+    <t>19.4%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -974,25 +974,25 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.4%</t>
+    <t>5.3%</t>
   </si>
   <si>
-    <t>1.3%</t>
+    <t>1.2%</t>
   </si>
   <si>
-    <t>7.7%</t>
+    <t>7.6%</t>
   </si>
   <si>
     <t>2.5%</t>
   </si>
   <si>
-    <t>5.5%</t>
+    <t>5.4%</t>
   </si>
   <si>
-    <t>1509.0</t>
+    <t>1521.0</t>
   </si>
   <si>
-    <t>1204.0</t>
+    <t>1213.0</t>
   </si>
   <si>
     <t>94.0</t>
@@ -1001,25 +1001,25 @@
     <t>11.0</t>
   </si>
   <si>
-    <t>327.0</t>
+    <t>329.0</t>
   </si>
   <si>
-    <t>76.0</t>
+    <t>77.0</t>
   </si>
   <si>
-    <t>14.0</t>
+    <t>15.0</t>
   </si>
   <si>
-    <t>469.0</t>
+    <t>476.0</t>
   </si>
   <si>
-    <t>153.0</t>
+    <t>154.0</t>
   </si>
   <si>
     <t>336.0</t>
   </si>
   <si>
-    <t>0.7%</t>
+    <t>0.6%</t>
   </si>
   <si>
     <t>40.0</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>6172.8400000000001</v>
+      </c>
+      <c r="N6" s="6">
+        <v>66</v>
+      </c>
+      <c r="O6" s="6">
+        <v>49</v>
+      </c>
+      <c r="P6" s="7">
+        <v>4.5819887096774199</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>13.454761224489797</v>
+      </c>
+      <c r="R6" s="8">
+        <v>2.1364583333333331</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.040816326530612242</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9132,7 +9190,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9220,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>560.60000000000002</v>
+      </c>
+      <c r="N51" s="6">
+        <v>5</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>7.306659999999999</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>18.2667</v>
+      </c>
+      <c r="R51" s="8">
+        <v>4.7000000000000002</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -10201,33 +10271,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>41</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24124,7 +24240,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24154,35 +24270,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2411.0300000000002</v>
+      </c>
+      <c r="N151" s="6">
+        <v>30</v>
+      </c>
+      <c r="O151" s="6">
+        <v>28</v>
+      </c>
+      <c r="P151" s="7">
+        <v>2.7548387096774194</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>11.567857142857141</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.0493814814814817</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -25006,7 +25180,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25036,35 +25210,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>2315.3200000000002</v>
+      </c>
+      <c r="N157" s="6">
+        <v>29</v>
+      </c>
+      <c r="O157" s="6">
+        <v>20</v>
+      </c>
+      <c r="P157" s="7">
+        <v>6.8833346153846158</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>18.244999999999997</v>
+      </c>
+      <c r="R157" s="8">
+        <v>4.5973684210526313</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25105,7 +25337,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,35 +25367,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>3665.52</v>
+      </c>
+      <c r="N158" s="6">
+        <v>32</v>
+      </c>
+      <c r="O158" s="6">
+        <v>29</v>
+      </c>
+      <c r="P158" s="7">
+        <v>9.6295709677419357</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>21.214368965517238</v>
+      </c>
+      <c r="R158" s="8">
+        <v>4.1068965517241374</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26088,7 +26378,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26118,35 +26408,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>3587.5500000000002</v>
+      </c>
+      <c r="N165" s="6">
+        <v>44</v>
+      </c>
+      <c r="O165" s="6">
+        <v>23</v>
+      </c>
+      <c r="P165" s="7">
+        <v>3.9821977272727271</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>12.250726086956522</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.1543478260869566</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
